--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h5.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Summary_Statistics_h5.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>1.0358</v>
       </c>
       <c r="F2">
-        <v>1.0444</v>
+        <v>1.1311</v>
       </c>
       <c r="G2">
-        <v>0.0086</v>
+        <v>0.0953</v>
       </c>
       <c r="H2">
-        <v>0.0405</v>
+        <v>0.5301</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M2">
         <v>36</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.8925</v>
+        <v>1.0381</v>
       </c>
       <c r="F3">
-        <v>0.9111</v>
+        <v>0.9204</v>
       </c>
       <c r="G3">
-        <v>0.0186</v>
+        <v>-0.1176</v>
       </c>
       <c r="H3">
-        <v>0.1271</v>
+        <v>-0.1544</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N3">
         <v>5</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>1.6294</v>
+        <v>1.0312</v>
       </c>
       <c r="F4">
-        <v>1.5966</v>
+        <v>1.5523</v>
       </c>
       <c r="G4">
-        <v>-0.0328</v>
+        <v>0.5211</v>
       </c>
       <c r="H4">
-        <v>-0.3183</v>
+        <v>1.8989</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
         <v>3</v>
       </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
       <c r="M4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N4">
         <v>5</v>
